--- a/Excel/ExclusiveAttrConfig.xlsx
+++ b/Excel/ExclusiveAttrConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -60,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -204,6 +209,18 @@
   </si>
   <si>
     <t>10,20,30,10,10</t>
+  </si>
+  <si>
+    <t>15,30,45,15</t>
+  </si>
+  <si>
+    <t>20,40,60,20</t>
+  </si>
+  <si>
+    <t>40,80,120,40,40</t>
+  </si>
+  <si>
+    <t>15,30,45,15,15</t>
   </si>
   <si>
     <t>Name</t>
@@ -1229,7 +1246,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="5" customWidth="1"/>
@@ -1736,9 +1753,64 @@
       <c r="H31" s="4"/>
     </row>
     <row r="32" customHeight="1" spans="1:21">
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="C32" s="4">
+        <v>25</v>
+      </c>
+      <c r="D32" s="4">
+        <v>5</v>
+      </c>
+      <c r="E32" s="4">
+        <v>1</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:8">
+      <c r="C33" s="4">
+        <v>26</v>
+      </c>
+      <c r="D33" s="4">
+        <v>5</v>
+      </c>
+      <c r="E33" s="4">
+        <v>2</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:8">
+      <c r="C34" s="4">
+        <v>27</v>
+      </c>
+      <c r="D34" s="4">
+        <v>5</v>
+      </c>
+      <c r="E34" s="4">
+        <v>3</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1788,13 +1860,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>2</v>
@@ -1806,13 +1878,13 @@
         <v>4</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12 16374:16384">
@@ -1822,13 +1894,13 @@
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>2</v>
@@ -1840,13 +1912,13 @@
         <v>4</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12 16374:16384">
@@ -1858,7 +1930,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>7</v>
@@ -1890,7 +1962,7 @@
         <v>1000001</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -1922,7 +1994,7 @@
         <v>1000002</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -1954,7 +2026,7 @@
         <v>1000003</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -1986,7 +2058,7 @@
         <v>1000004</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E9">
         <v>16</v>
@@ -2018,7 +2090,7 @@
         <v>1000005</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E10">
         <v>16</v>
@@ -2050,7 +2122,7 @@
         <v>1000006</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E11">
         <v>16</v>
